--- a/zenteno_parameters.xlsx
+++ b/zenteno_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/cristobal_torrealba_conchaytoro_cl/Documents/Documentos/Proyectos I+D/PI-4497/Resultados/2025/dFBA/Calibración modelo piloto 24_25/SB_Calibration_2025/Calibración data 2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{41C3D8F6-5C7C-42FD-A0CB-62F8879C6ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38CB918E-39AF-4445-A67B-886F99A04C98}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B175C98-77CA-4BD1-A3A0-86EA0CCEB32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{708A1B0C-CE8A-4E9F-84D7-5F51B80A027D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{708A1B0C-CE8A-4E9F-84D7-5F51B80A027D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,64 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Cristobal Torrealba</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{8E5FD2E3-F0DB-440F-A779-B13AA35D47A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Cristobal Torrealba:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+2025</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{3EB21962-1FF1-4D99-855F-32BCFA630B5B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Cristobal Torrealba:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+2025+2024</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
@@ -86,15 +144,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,7 +192,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,11 +506,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DDF53A-1D96-4DCA-89AC-6729FF7FF5EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DDF53A-1D96-4DCA-89AC-6729FF7FF5EF}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -533,7 +604,7 @@
         <v>0.62651656888274598</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -580,7 +651,7 @@
         <v>0.62651659999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -627,7 +698,7 @@
         <v>1.1353544376279339</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -674,37 +745,85 @@
         <v>0.57803400000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.14166500000000001</v>
+      </c>
+      <c r="C6">
+        <v>1.4118200000000001</v>
+      </c>
+      <c r="D6">
+        <v>8.4948200000000007</v>
+      </c>
+      <c r="E6">
+        <v>0.226882</v>
+      </c>
+      <c r="F6">
+        <v>3.1514000000000002</v>
+      </c>
+      <c r="G6">
+        <v>2.9762499999999998</v>
+      </c>
+      <c r="H6">
+        <v>29.5276</v>
+      </c>
+      <c r="I6">
+        <v>2.9980899999999999</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3.1173600000000003E-5</v>
+      </c>
+      <c r="K6">
+        <v>9.8057599999999994</v>
+      </c>
+      <c r="L6">
+        <v>0.394345</v>
+      </c>
+      <c r="M6">
+        <v>0.18622</v>
+      </c>
+      <c r="N6">
+        <v>0.14133000000000001</v>
+      </c>
+      <c r="O6">
+        <v>0.96931999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>